--- a/results/Int Task Remove ACC -0.2/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_3_permute.xlsx
@@ -440,787 +440,787 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7712626430183023</v>
+        <v>0.7685126922868757</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7709467870486244</v>
+        <v>0.7763832694253487</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7712849533157027</v>
+        <v>0.782585325525831</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7782149861572867</v>
+        <v>0.7783083588834441</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7797684439022032</v>
+        <v>0.7746073284369117</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7942831515526108</v>
+        <v>0.7819724120778034</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7938933410785871</v>
+        <v>0.7819724120778034</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7858742352009394</v>
+        <v>0.7803262013372132</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7674124641021118</v>
+        <v>0.7825818137197587</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7654427540492157</v>
+        <v>0.7205870748184087</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7759845761477305</v>
+        <v>0.7086361921775965</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7695670604158722</v>
+        <v>0.7017877571829862</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7781726379075916</v>
+        <v>0.7066036827690549</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.781557812384446</v>
+        <v>0.7091416856751778</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.785459635507582</v>
+        <v>0.7122409578223827</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7766861110548764</v>
+        <v>0.7151952130364851</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7748579061290106</v>
+        <v>0.7119139467040048</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7636162017379722</v>
+        <v>0.7192379215561681</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6997263270185552</v>
+        <v>0.7079005720938669</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.687559984746367</v>
+        <v>0.7068937166352601</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6966939857635513</v>
+        <v>0.7013498143080895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6720454452494973</v>
+        <v>0.6848918384387419</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6627629154931381</v>
+        <v>0.6845648273203639</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.658578701846425</v>
+        <v>0.7254558840723895</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6526555244634477</v>
+        <v>0.7231556510950431</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6555540039340491</v>
+        <v>0.7014062097820739</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6575049154956171</v>
+        <v>0.7023314673937069</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6581366274349727</v>
+        <v>0.6944573784491617</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.65767224272612</v>
+        <v>0.718774776308282</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6647884012895352</v>
+        <v>0.7042600686578745</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6552499228435549</v>
+        <v>0.7158386998550244</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6285277641322307</v>
+        <v>0.6784080115451658</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6135932923677712</v>
+        <v>0.7068497157709426</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6142584697532275</v>
+        <v>0.709338966545709</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6091266881974808</v>
+        <v>0.7071079368056694</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.59693452382182</v>
+        <v>0.6739265338432752</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5731449297576812</v>
+        <v>0.6320837776456605</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5748169626017442</v>
+        <v>0.6574344727973436</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5766897881224108</v>
+        <v>0.6428228806147065</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5697744222355993</v>
+        <v>0.6346252923578555</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5734126533264861</v>
+        <v>0.6421019274857493</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5771547925617468</v>
+        <v>0.6415148361411944</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5771547925617468</v>
+        <v>0.6415148361411944</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5373011646388397</v>
+        <v>0.6435215234462635</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.533291301834774</v>
+        <v>0.6435215234462635</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5152205806709368</v>
+        <v>0.6266584504176363</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5143287885054043</v>
+        <v>0.6407903712061649</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5119504694871565</v>
+        <v>0.6376464784641591</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5119504694871565</v>
+        <v>0.614294827274917</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5022035550219446</v>
+        <v>0.6181966503980529</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5672957068790496</v>
+        <v>0.6185013512190305</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5684587344194592</v>
+        <v>0.6185013512190305</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.550019273618032</v>
+        <v>0.6128012768100571</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5663468995090495</v>
+        <v>0.6128682077022584</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.542672368737985</v>
+        <v>0.5998435387106383</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5315498591765765</v>
+        <v>0.572749128555652</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4573753505092325</v>
+        <v>0.5747223504146204</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4713482071403694</v>
+        <v>0.5750382063842981</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4258021481511167</v>
+        <v>0.5648004653762776</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4118968421426644</v>
+        <v>0.5475727842466164</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4148211437167386</v>
+        <v>0.5475727842466164</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4138847309564053</v>
+        <v>0.5445739084377131</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4506502418808077</v>
+        <v>0.5445739084377131</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4515643443437405</v>
+        <v>0.5219655206748287</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4515643443437405</v>
+        <v>0.5219655206748287</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4846534074641166</v>
+        <v>0.5223148420906071</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4891423219318073</v>
+        <v>0.5078928874358734</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4878342774582952</v>
+        <v>0.5082198985542514</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4994093968493729</v>
+        <v>0.5072723306452179</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5076069851062238</v>
+        <v>0.5039687540153371</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.500223102974004</v>
+        <v>0.5043292305798157</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4997510749225234</v>
+        <v>0.5036863634917599</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4997064543277225</v>
+        <v>0.5027276404340262</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4997064543277225</v>
+        <v>0.5027276404340262</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4997064543277225</v>
+        <v>0.5036975186404601</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5000446205948008</v>
+        <v>0.5040914606510393</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5000446205948008</v>
+        <v>0.5021517042381715</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5000446205948008</v>
+        <v>0.5021517042381715</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5</v>
+        <v>0.5060423722126073</v>
       </c>
     </row>
     <row r="81">
@@ -1230,33 +1230,33 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.5060200619152068</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5</v>
+        <v>0.5060089067665066</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.5003604765644786</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1276,7 +1276,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1286,41 +1286,41 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.5003270111183781</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.5003270111183781</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.5003270111183781</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.5000223102974004</v>
       </c>
     </row>
   </sheetData>
